--- a/Databricks/ae outputs/hospital_model_performance_yes.xlsx
+++ b/Databricks/ae outputs/hospital_model_performance_yes.xlsx
@@ -408,19 +408,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>44.81705727879428</v>
+        <v>45.27530806122608</v>
       </c>
       <c r="C2">
-        <v>0.7048998886717373</v>
+        <v>0.6944755235990371</v>
       </c>
       <c r="D2">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E2">
         <v>500</v>
       </c>
       <c r="F2">
-        <v>0.03699600009256014</v>
+        <v>0.03730661508011378</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -445,19 +445,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>33.05907261717342</v>
+        <v>33.1791936317481</v>
       </c>
       <c r="C3">
-        <v>0.67137629052119</v>
+        <v>0.6835489389728053</v>
       </c>
       <c r="D3">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E3">
         <v>500</v>
       </c>
       <c r="F3">
-        <v>0.05129745540907494</v>
+        <v>0.05122775696601424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>28.55132505462418</v>
+        <v>28.72887586135961</v>
       </c>
       <c r="C4">
-        <v>0.5880289349904768</v>
+        <v>0.5901095459783033</v>
       </c>
       <c r="D4">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E4">
         <v>500</v>
       </c>
       <c r="F4">
-        <v>0.04533220447662775</v>
+        <v>0.0455522227775728</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -519,19 +519,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>14.73067385262597</v>
+        <v>14.59244462653156</v>
       </c>
       <c r="C5">
-        <v>0.5854049077208063</v>
+        <v>0.5972908244929592</v>
       </c>
       <c r="D5">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
       <c r="F5">
-        <v>0.08364563114597312</v>
+        <v>0.08262368616864467</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>28.59973474154552</v>
+        <v>28.59270068764518</v>
       </c>
       <c r="C6">
-        <v>0.3784159950015327</v>
+        <v>0.381061891224408</v>
       </c>
       <c r="D6">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E6">
         <v>500</v>
       </c>
       <c r="F6">
-        <v>0.0510315482946173</v>
+        <v>0.05097101520187745</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>35.8612545515846</v>
+        <v>35.95542038515872</v>
       </c>
       <c r="C7">
-        <v>0.6477075454785278</v>
+        <v>0.6536878938401242</v>
       </c>
       <c r="D7">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E7">
         <v>500</v>
       </c>
       <c r="F7">
-        <v>0.03327147488487037</v>
+        <v>0.03332126343939631</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>39.94585889356822</v>
+        <v>40.42800296917279</v>
       </c>
       <c r="C8">
-        <v>0.7478624886109133</v>
+        <v>0.7441010432334095</v>
       </c>
       <c r="D8">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E8">
         <v>500</v>
       </c>
       <c r="F8">
-        <v>0.03000399470284256</v>
+        <v>0.03033586680161238</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>61.55065370784428</v>
+        <v>63.44282167716962</v>
       </c>
       <c r="C9">
-        <v>0.5460642164950222</v>
+        <v>0.5197091982925484</v>
       </c>
       <c r="D9">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E9">
         <v>500</v>
       </c>
       <c r="F9">
-        <v>0.03830255539150215</v>
+        <v>0.03945056566334793</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -704,19 +704,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>61.44307200859443</v>
+        <v>61.4862375238831</v>
       </c>
       <c r="C10">
-        <v>0.5681051516974719</v>
+        <v>0.5680742357194616</v>
       </c>
       <c r="D10">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E10">
         <v>500</v>
       </c>
       <c r="F10">
-        <v>0.03173402286907961</v>
+        <v>0.03174236852304707</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>96.47226461734583</v>
+        <v>98.17339867472916</v>
       </c>
       <c r="C11">
-        <v>0.6903116955774782</v>
+        <v>0.6756320015271876</v>
       </c>
       <c r="D11">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E11">
         <v>500</v>
       </c>
       <c r="F11">
-        <v>0.06676718368997869</v>
+        <v>0.0679218931091536</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>14.46025430573647</v>
+        <v>14.223475897695</v>
       </c>
       <c r="C12">
-        <v>0.5203338449092897</v>
+        <v>0.5345831198325551</v>
       </c>
       <c r="D12">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E12">
         <v>500</v>
       </c>
       <c r="F12">
-        <v>0.07803243773240713</v>
+        <v>0.07661309195110061</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>29.37113737104123</v>
+        <v>30.71671419764695</v>
       </c>
       <c r="C13">
-        <v>0.758074007511885</v>
+        <v>0.7446230531593974</v>
       </c>
       <c r="D13">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E13">
         <v>500</v>
       </c>
       <c r="F13">
-        <v>0.03844729733167732</v>
+        <v>0.04012529286974468</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -852,19 +852,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>15.46723081544823</v>
+        <v>15.26930194173871</v>
       </c>
       <c r="C14">
-        <v>0.7952499253199332</v>
+        <v>0.7975715248648727</v>
       </c>
       <c r="D14">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E14">
         <v>500</v>
       </c>
       <c r="F14">
-        <v>0.08614895983314534</v>
+        <v>0.08500576348206673</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>40.59821723786782</v>
+        <v>40.38930612839602</v>
       </c>
       <c r="C15">
-        <v>0.671131384476028</v>
+        <v>0.6769270038737748</v>
       </c>
       <c r="D15">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E15">
         <v>500</v>
       </c>
       <c r="F15">
-        <v>0.03273764357512661</v>
+        <v>0.03253633605754658</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>45.07467875937916</v>
+        <v>44.52310622171513</v>
       </c>
       <c r="C16">
-        <v>0.6616126327488164</v>
+        <v>0.6699580039480477</v>
       </c>
       <c r="D16">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E16">
         <v>500</v>
       </c>
       <c r="F16">
-        <v>0.03686560521004065</v>
+        <v>0.03637944597531986</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>44.66516068329877</v>
+        <v>45.53806373749828</v>
       </c>
       <c r="C17">
-        <v>0.6463380031135497</v>
+        <v>0.6278835104090887</v>
       </c>
       <c r="D17">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E17">
         <v>500</v>
       </c>
       <c r="F17">
-        <v>0.03315899085619805</v>
+        <v>0.03380903374921916</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>32.94325883413913</v>
+        <v>33.16454577245212</v>
       </c>
       <c r="C18">
-        <v>0.7811537868798101</v>
+        <v>0.7849860793492619</v>
       </c>
       <c r="D18">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E18">
         <v>500</v>
       </c>
       <c r="F18">
-        <v>0.03019509696818351</v>
+        <v>0.03034785974956271</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>32.75861675748062</v>
+        <v>34.26618618874139</v>
       </c>
       <c r="C19">
-        <v>0.6609110255278573</v>
+        <v>0.6314023594422881</v>
       </c>
       <c r="D19">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E19">
         <v>500</v>
       </c>
       <c r="F19">
-        <v>0.09328988416600216</v>
+        <v>0.09743939200589967</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>28.53684106819441</v>
+        <v>29.04037459588135</v>
       </c>
       <c r="C20">
-        <v>0.6674169627095471</v>
+        <v>0.6639293514935465</v>
       </c>
       <c r="D20">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E20">
         <v>500</v>
       </c>
       <c r="F20">
-        <v>0.05633673671556894</v>
+        <v>0.05720813444765447</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>14.31966862399</v>
+        <v>14.78717065927348</v>
       </c>
       <c r="C21">
-        <v>0.5176833858337517</v>
+        <v>0.4855729757418473</v>
       </c>
       <c r="D21">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E21">
         <v>500</v>
       </c>
       <c r="F21">
-        <v>0.09727857139220231</v>
+        <v>0.1005382829703119</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>35.41084732186489</v>
+        <v>35.91501540847731</v>
       </c>
       <c r="C22">
-        <v>0.7461332638156679</v>
+        <v>0.7408049172393834</v>
       </c>
       <c r="D22">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E22">
         <v>500</v>
       </c>
       <c r="F22">
-        <v>0.03217231275789761</v>
+        <v>0.03259864644361368</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>73.85715158652863</v>
+        <v>73.05844344938347</v>
       </c>
       <c r="C23">
-        <v>0.6612365378391437</v>
+        <v>0.6676581859893509</v>
       </c>
       <c r="D23">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E23">
         <v>500</v>
       </c>
       <c r="F23">
-        <v>0.03074594099607405</v>
+        <v>0.03038952474254048</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>75.84421773075616</v>
+        <v>77.03439432735763</v>
       </c>
       <c r="C24">
-        <v>0.6920940091069966</v>
+        <v>0.6840407355801199</v>
       </c>
       <c r="D24">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E24">
         <v>500</v>
       </c>
       <c r="F24">
-        <v>0.07375321443501742</v>
+        <v>0.0748187614062473</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>40.39950244213524</v>
+        <v>40.73550964778391</v>
       </c>
       <c r="C25">
-        <v>0.6982971089196301</v>
+        <v>0.6917274894918499</v>
       </c>
       <c r="D25">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E25">
         <v>500</v>
       </c>
       <c r="F25">
-        <v>0.03403612660918777</v>
+        <v>0.03432382006048527</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>26.14707562923531</v>
+        <v>26.66906847937193</v>
       </c>
       <c r="C26">
-        <v>0.6100253932865453</v>
+        <v>0.6056951176138359</v>
       </c>
       <c r="D26">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E26">
         <v>500</v>
       </c>
       <c r="F26">
-        <v>0.05810112295247771</v>
+        <v>0.0591017384969682</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1333,19 +1333,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>35.88443471364169</v>
+        <v>36.51729447628237</v>
       </c>
       <c r="C27">
-        <v>0.7220886434281553</v>
+        <v>0.7194280881189602</v>
       </c>
       <c r="D27">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E27">
         <v>500</v>
       </c>
       <c r="F27">
-        <v>0.03059730338425668</v>
+        <v>0.03109795714455748</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>11.45898945891048</v>
+        <v>11.5145896904545</v>
       </c>
       <c r="C28">
-        <v>0.5058819976701171</v>
+        <v>0.4985111858293225</v>
       </c>
       <c r="D28">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E28">
         <v>500</v>
       </c>
       <c r="F28">
-        <v>0.1029458807769061</v>
+        <v>0.1028088365219152</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>18.44840142933608</v>
+        <v>18.61463110993078</v>
       </c>
       <c r="C29">
-        <v>0.4460759773766749</v>
+        <v>0.4383896946656952</v>
       </c>
       <c r="D29">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E29">
         <v>500</v>
       </c>
       <c r="F29">
-        <v>0.06971615288381525</v>
+        <v>0.07040329466690917</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>32.48977879442344</v>
+        <v>33.68170058306125</v>
       </c>
       <c r="C30">
-        <v>0.7829583335185124</v>
+        <v>0.7663166787349669</v>
       </c>
       <c r="D30">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E30">
         <v>500</v>
       </c>
       <c r="F30">
-        <v>0.04654425768632919</v>
+        <v>0.04821866314931748</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>13.6256210546698</v>
+        <v>13.62838786878143</v>
       </c>
       <c r="C31">
-        <v>0.4715510520880196</v>
+        <v>0.4654822964751263</v>
       </c>
       <c r="D31">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E31">
         <v>500</v>
       </c>
       <c r="F31">
-        <v>0.08446812080468838</v>
+        <v>0.0844176651931456</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1518,19 +1518,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>41.1253959650297</v>
+        <v>39.74560436140318</v>
       </c>
       <c r="C32">
-        <v>0.7547636114756577</v>
+        <v>0.7677021549659526</v>
       </c>
       <c r="D32">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E32">
         <v>1000</v>
       </c>
       <c r="F32">
-        <v>0.03394857327343345</v>
+        <v>0.03275016839271851</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1555,19 +1555,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>34.57353902991185</v>
+        <v>33.72269928814519</v>
       </c>
       <c r="C33">
-        <v>0.6424588135871219</v>
+        <v>0.671164049607159</v>
       </c>
       <c r="D33">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E33">
         <v>1000</v>
       </c>
       <c r="F33">
-        <v>0.0536474388516121</v>
+        <v>0.05206691466178544</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>28.8873388660721</v>
+        <v>28.09677310985129</v>
       </c>
       <c r="C34">
-        <v>0.5778532726089152</v>
+        <v>0.6051158694374654</v>
       </c>
       <c r="D34">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E34">
         <v>1000</v>
       </c>
       <c r="F34">
-        <v>0.04586570850064014</v>
+        <v>0.04454996687678584</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1629,19 +1629,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>16.22296703164079</v>
+        <v>15.54028459369505</v>
       </c>
       <c r="C35">
-        <v>0.4972704173525279</v>
+        <v>0.5467177241228819</v>
       </c>
       <c r="D35">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E35">
         <v>1000</v>
       </c>
       <c r="F35">
-        <v>0.09211936466708247</v>
+        <v>0.0879904382098089</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>30.02945218125796</v>
+        <v>29.787155853609</v>
       </c>
       <c r="C36">
-        <v>0.3296731046365465</v>
+        <v>0.3481064955047052</v>
       </c>
       <c r="D36">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E36">
         <v>1000</v>
       </c>
       <c r="F36">
-        <v>0.05358264519225234</v>
+        <v>0.05310032061752887</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1703,19 +1703,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>34.61392631118017</v>
+        <v>33.47579603377814</v>
       </c>
       <c r="C37">
-        <v>0.673199423125903</v>
+        <v>0.6980488259896308</v>
       </c>
       <c r="D37">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E37">
         <v>1000</v>
       </c>
       <c r="F37">
-        <v>0.03211422451137579</v>
+        <v>0.03102330070226199</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>34.9434910169571</v>
+        <v>35.45271700418498</v>
       </c>
       <c r="C38">
-        <v>0.8076129210327218</v>
+        <v>0.8031125331861653</v>
       </c>
       <c r="D38">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E38">
         <v>1000</v>
       </c>
       <c r="F38">
-        <v>0.02624663352877412</v>
+        <v>0.02660257301391555</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1777,19 +1777,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>62.43301533087152</v>
+        <v>59.39905248533747</v>
       </c>
       <c r="C39">
-        <v>0.5365616488926956</v>
+        <v>0.5782402270795359</v>
       </c>
       <c r="D39">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E39">
         <v>1000</v>
       </c>
       <c r="F39">
-        <v>0.03885164306003863</v>
+        <v>0.03693603402978402</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>61.03438943781005</v>
+        <v>59.35550098076133</v>
       </c>
       <c r="C40">
-        <v>0.5785092002660625</v>
+        <v>0.596099506090804</v>
       </c>
       <c r="D40">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E40">
         <v>1000</v>
       </c>
       <c r="F40">
-        <v>0.03152294712655079</v>
+        <v>0.03064237237267239</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>86.63973985965264</v>
+        <v>82.9981182189089</v>
       </c>
       <c r="C41">
-        <v>0.7500293278621409</v>
+        <v>0.767675930599074</v>
       </c>
       <c r="D41">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E41">
         <v>1000</v>
       </c>
       <c r="F41">
-        <v>0.05996222281094147</v>
+        <v>0.05742277836996944</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>15.91131269296743</v>
+        <v>15.29919295852008</v>
       </c>
       <c r="C42">
-        <v>0.4347662091017626</v>
+        <v>0.4819730530500739</v>
       </c>
       <c r="D42">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E42">
         <v>1000</v>
       </c>
       <c r="F42">
-        <v>0.0858628410471516</v>
+        <v>0.08240731628045145</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1925,19 +1925,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>30.1953349999208</v>
+        <v>29.33336444744912</v>
       </c>
       <c r="C43">
-        <v>0.7455040383504619</v>
+        <v>0.766297866534882</v>
       </c>
       <c r="D43">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E43">
         <v>1000</v>
       </c>
       <c r="F43">
-        <v>0.03952618545566396</v>
+        <v>0.03831822087920514</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1962,19 +1962,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>16.40044935166527</v>
+        <v>16.26588317681638</v>
       </c>
       <c r="C44">
-        <v>0.7680699953514544</v>
+        <v>0.773152915991598</v>
       </c>
       <c r="D44">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E44">
         <v>1000</v>
       </c>
       <c r="F44">
-        <v>0.09134677495282477</v>
+        <v>0.09055383300632634</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1999,19 +1999,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>36.50998219637515</v>
+        <v>34.40196329441742</v>
       </c>
       <c r="C45">
-        <v>0.7314834710785216</v>
+        <v>0.7648865809083037</v>
       </c>
       <c r="D45">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E45">
         <v>1000</v>
       </c>
       <c r="F45">
-        <v>0.02944096724927819</v>
+        <v>0.02771312374687232</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2036,19 +2036,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>39.9757352686627</v>
+        <v>39.01980806289754</v>
       </c>
       <c r="C46">
-        <v>0.7307253253551107</v>
+        <v>0.7447725003949881</v>
       </c>
       <c r="D46">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E46">
         <v>1000</v>
       </c>
       <c r="F46">
-        <v>0.0326952895718411</v>
+        <v>0.03188274852887945</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>39.69428382428703</v>
+        <v>40.76792306262632</v>
       </c>
       <c r="C47">
-        <v>0.7259554569270492</v>
+        <v>0.7056395443059637</v>
       </c>
       <c r="D47">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E47">
         <v>1000</v>
       </c>
       <c r="F47">
-        <v>0.02946865911231405</v>
+        <v>0.0302675163058135</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2110,19 +2110,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>31.06168099878531</v>
+        <v>30.06542917501526</v>
       </c>
       <c r="C48">
-        <v>0.8064802763782867</v>
+        <v>0.8288498171778683</v>
       </c>
       <c r="D48">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E48">
         <v>1000</v>
       </c>
       <c r="F48">
-        <v>0.02847048236712842</v>
+        <v>0.02751195310118403</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2147,19 +2147,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>33.97586476936002</v>
+        <v>33.50388591335997</v>
       </c>
       <c r="C49">
-        <v>0.6364211551783211</v>
+        <v>0.6471842335626068</v>
       </c>
       <c r="D49">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E49">
         <v>1000</v>
       </c>
       <c r="F49">
-        <v>0.096756359166159</v>
+        <v>0.09527171349770606</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>29.28836904522342</v>
+        <v>29.14259226024808</v>
       </c>
       <c r="C50">
-        <v>0.6513916680017532</v>
+        <v>0.6594071658102187</v>
       </c>
       <c r="D50">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E50">
         <v>1000</v>
       </c>
       <c r="F50">
-        <v>0.05782038494681818</v>
+        <v>0.05740949830633027</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>14.34549560344652</v>
+        <v>14.84361451656922</v>
       </c>
       <c r="C51">
-        <v>0.5096006032694144</v>
+        <v>0.4810844875263769</v>
       </c>
       <c r="D51">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E51">
         <v>1000</v>
       </c>
       <c r="F51">
-        <v>0.09745402319425708</v>
+        <v>0.1009220459380556</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>33.63375335902244</v>
+        <v>32.86054533767783</v>
       </c>
       <c r="C52">
-        <v>0.7718749075349061</v>
+        <v>0.7828112504478768</v>
       </c>
       <c r="D52">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E52">
         <v>1000</v>
       </c>
       <c r="F52">
-        <v>0.03055774470610641</v>
+        <v>0.02982622413561463</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2295,19 +2295,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>77.14447190001842</v>
+        <v>75.30763644850383</v>
       </c>
       <c r="C53">
-        <v>0.6304466597738925</v>
+        <v>0.6502594797232778</v>
       </c>
       <c r="D53">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E53">
         <v>1000</v>
       </c>
       <c r="F53">
-        <v>0.03211441722650842</v>
+        <v>0.03132510320644345</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2332,19 +2332,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>67.76025964470385</v>
+        <v>65.94697299856651</v>
       </c>
       <c r="C54">
-        <v>0.7548705552131058</v>
+        <v>0.7654812823707504</v>
       </c>
       <c r="D54">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E54">
         <v>1000</v>
       </c>
       <c r="F54">
-        <v>0.06589212875119038</v>
+        <v>0.06405023212458384</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>36.25069832988252</v>
+        <v>35.68167478721766</v>
       </c>
       <c r="C55">
-        <v>0.7571621680613008</v>
+        <v>0.7624097171365614</v>
       </c>
       <c r="D55">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E55">
         <v>1000</v>
       </c>
       <c r="F55">
-        <v>0.03054080578825419</v>
+        <v>0.03006544892755111</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2406,19 +2406,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>26.92781103276152</v>
+        <v>26.63310969552934</v>
       </c>
       <c r="C56">
-        <v>0.5842493545828912</v>
+        <v>0.6044433076012645</v>
       </c>
       <c r="D56">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E56">
         <v>1000</v>
       </c>
       <c r="F56">
-        <v>0.05983598631987126</v>
+        <v>0.05902204967540408</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2443,19 +2443,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>33.21174832831714</v>
+        <v>31.02421753930838</v>
       </c>
       <c r="C57">
-        <v>0.7613455160139662</v>
+        <v>0.79624444250657</v>
       </c>
       <c r="D57">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E57">
         <v>1000</v>
       </c>
       <c r="F57">
-        <v>0.02831840455708191</v>
+        <v>0.026420078522177</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2480,19 +2480,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>10.98386879036859</v>
+        <v>11.42912141420069</v>
       </c>
       <c r="C58">
-        <v>0.5160059355097142</v>
+        <v>0.4942745927819516</v>
       </c>
       <c r="D58">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E58">
         <v>1000</v>
       </c>
       <c r="F58">
-        <v>0.09867746636970685</v>
+        <v>0.1020457269125061</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2517,19 +2517,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>18.24710416463728</v>
+        <v>18.68784111576019</v>
       </c>
       <c r="C59">
-        <v>0.4527148682990713</v>
+        <v>0.4482613638956492</v>
       </c>
       <c r="D59">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E59">
         <v>1000</v>
       </c>
       <c r="F59">
-        <v>0.06895545440624853</v>
+        <v>0.07068018576308695</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2554,19 +2554,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>32.34936494919539</v>
+        <v>33.24004005138409</v>
       </c>
       <c r="C60">
-        <v>0.7847182435005258</v>
+        <v>0.7721732846664813</v>
       </c>
       <c r="D60">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E60">
         <v>1000</v>
       </c>
       <c r="F60">
-        <v>0.04634310340219647</v>
+        <v>0.04758638271113796</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>14.02843521899512</v>
+        <v>14.23781639148041</v>
       </c>
       <c r="C61">
-        <v>0.4412181182810603</v>
+        <v>0.4383694640997851</v>
       </c>
       <c r="D61">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E61">
         <v>1000</v>
       </c>
       <c r="F61">
-        <v>0.08696525142042716</v>
+        <v>0.08819261887686083</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2628,19 +2628,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>33.24250211409304</v>
+        <v>33.13697464871367</v>
       </c>
       <c r="C62">
-        <v>0.8455644233357791</v>
+        <v>0.8442548412365115</v>
       </c>
       <c r="D62">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E62">
         <v>2000</v>
       </c>
       <c r="F62">
-        <v>0.02744132894847226</v>
+        <v>0.02730469236050896</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2665,19 +2665,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>34.26608048985912</v>
+        <v>33.98609721848557</v>
       </c>
       <c r="C63">
-        <v>0.6497920406505006</v>
+        <v>0.6689050976691344</v>
       </c>
       <c r="D63">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E63">
         <v>2000</v>
       </c>
       <c r="F63">
-        <v>0.05317035829550778</v>
+        <v>0.05247359377854121</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2702,19 +2702,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>28.46569740651707</v>
+        <v>28.1268663276128</v>
       </c>
       <c r="C64">
-        <v>0.5912857340766019</v>
+        <v>0.6060157035213528</v>
       </c>
       <c r="D64">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E64">
         <v>2000</v>
       </c>
       <c r="F64">
-        <v>0.04519624966383297</v>
+        <v>0.0445976823866506</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2739,19 +2739,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>16.82289152103777</v>
+        <v>16.5252288103354</v>
       </c>
       <c r="C65">
-        <v>0.4675361997779036</v>
+        <v>0.495536611335493</v>
       </c>
       <c r="D65">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E65">
         <v>2000</v>
       </c>
       <c r="F65">
-        <v>0.09552593405131948</v>
+        <v>0.0935672777272501</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2776,19 +2776,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>30.30396259050714</v>
+        <v>31.00489727384567</v>
       </c>
       <c r="C66">
-        <v>0.3207088175145437</v>
+        <v>0.3137109291755737</v>
       </c>
       <c r="D66">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E66">
         <v>2000</v>
       </c>
       <c r="F66">
-        <v>0.05407246411307698</v>
+        <v>0.05527113746763702</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2813,19 +2813,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>30.67403173515297</v>
+        <v>31.6304353831306</v>
       </c>
       <c r="C67">
-        <v>0.745977831698224</v>
+        <v>0.7317961583480342</v>
       </c>
       <c r="D67">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E67">
         <v>2000</v>
       </c>
       <c r="F67">
-        <v>0.02845885592278485</v>
+        <v>0.02931313439848256</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2850,19 +2850,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>29.00272055304322</v>
+        <v>27.97115526724511</v>
       </c>
       <c r="C68">
-        <v>0.8692664059369007</v>
+        <v>0.87992083952691</v>
       </c>
       <c r="D68">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E68">
         <v>2000</v>
       </c>
       <c r="F68">
-        <v>0.02178442266468938</v>
+        <v>0.02098865088936962</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>57.30858184416392</v>
+        <v>57.58950079605625</v>
       </c>
       <c r="C69">
-        <v>0.5989136873669778</v>
+        <v>0.5971606438138506</v>
       </c>
       <c r="D69">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E69">
         <v>2000</v>
       </c>
       <c r="F69">
-        <v>0.03566274276977783</v>
+        <v>0.03581080290273123</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2924,19 +2924,19 @@
         </is>
       </c>
       <c r="B70">
-        <v>56.48607022747159</v>
+        <v>56.61240750022242</v>
       </c>
       <c r="C70">
-        <v>0.6279625032510713</v>
+        <v>0.6276421278705592</v>
       </c>
       <c r="D70">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E70">
         <v>2000</v>
       </c>
       <c r="F70">
-        <v>0.02917383825034477</v>
+        <v>0.02922624597335234</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2961,19 +2961,19 @@
         </is>
       </c>
       <c r="B71">
-        <v>73.38828353806529</v>
+        <v>72.83249765026261</v>
       </c>
       <c r="C71">
-        <v>0.8214794530287809</v>
+        <v>0.8223953949526834</v>
       </c>
       <c r="D71">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E71">
         <v>2000</v>
       </c>
       <c r="F71">
-        <v>0.05079106442782967</v>
+        <v>0.05038962883075989</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2998,19 +2998,19 @@
         </is>
       </c>
       <c r="B72">
-        <v>15.54743431423089</v>
+        <v>16.28453677611071</v>
       </c>
       <c r="C72">
-        <v>0.4586758889280891</v>
+        <v>0.4266307120557788</v>
       </c>
       <c r="D72">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E72">
         <v>2000</v>
       </c>
       <c r="F72">
-        <v>0.08389922987333813</v>
+        <v>0.08771475568861703</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3035,19 +3035,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>29.67742727439723</v>
+        <v>30.44947938490159</v>
       </c>
       <c r="C73">
-        <v>0.7578165654184502</v>
+        <v>0.7545734483777865</v>
       </c>
       <c r="D73">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E73">
         <v>2000</v>
       </c>
       <c r="F73">
-        <v>0.03884823580522891</v>
+        <v>0.03977620360657016</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3072,19 +3072,19 @@
         </is>
       </c>
       <c r="B74">
-        <v>16.95557114760163</v>
+        <v>17.02671247329242</v>
       </c>
       <c r="C74">
-        <v>0.7543175910614675</v>
+        <v>0.7496688913991587</v>
       </c>
       <c r="D74">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E74">
         <v>2000</v>
       </c>
       <c r="F74">
-        <v>0.09443867717315374</v>
+        <v>0.09478944740921402</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="B75">
-        <v>29.52729716380677</v>
+        <v>28.81577248033093</v>
       </c>
       <c r="C75">
-        <v>0.8283242644817369</v>
+        <v>0.8371518966319592</v>
       </c>
       <c r="D75">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E75">
         <v>2000</v>
       </c>
       <c r="F75">
-        <v>0.02381026054966547</v>
+        <v>0.02321306670130416</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3146,19 +3146,19 @@
         </is>
       </c>
       <c r="B76">
-        <v>33.44012042779901</v>
+        <v>32.91683231705419</v>
       </c>
       <c r="C76">
-        <v>0.8124274774535077</v>
+        <v>0.8190106270588708</v>
       </c>
       <c r="D76">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E76">
         <v>2000</v>
       </c>
       <c r="F76">
-        <v>0.02734995149823301</v>
+        <v>0.02689605969973596</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3183,19 +3183,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>34.06364123714877</v>
+        <v>32.44338250824436</v>
       </c>
       <c r="C77">
-        <v>0.8018733514915142</v>
+        <v>0.8193597308790289</v>
       </c>
       <c r="D77">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E77">
         <v>2000</v>
       </c>
       <c r="F77">
-        <v>0.02528852356135766</v>
+        <v>0.02408708943979179</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3220,19 +3220,19 @@
         </is>
       </c>
       <c r="B78">
-        <v>28.49179732823116</v>
+        <v>27.37467657883971</v>
       </c>
       <c r="C78">
-        <v>0.8411033890387655</v>
+        <v>0.8582348937043028</v>
       </c>
       <c r="D78">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E78">
         <v>2000</v>
       </c>
       <c r="F78">
-        <v>0.02611498113939563</v>
+        <v>0.02504972783900853</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3257,19 +3257,19 @@
         </is>
       </c>
       <c r="B79">
-        <v>34.79458542515181</v>
+        <v>34.43170710439666</v>
       </c>
       <c r="C79">
-        <v>0.6266286393911232</v>
+        <v>0.6288378892933305</v>
       </c>
       <c r="D79">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E79">
         <v>2000</v>
       </c>
       <c r="F79">
-        <v>0.09908790923460588</v>
+        <v>0.09791006759544074</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3294,19 +3294,19 @@
         </is>
       </c>
       <c r="B80">
-        <v>29.44141817649204</v>
+        <v>29.62616920906565</v>
       </c>
       <c r="C80">
-        <v>0.647723859306977</v>
+        <v>0.6493711291860578</v>
       </c>
       <c r="D80">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E80">
         <v>2000</v>
       </c>
       <c r="F80">
-        <v>0.05812253081475859</v>
+        <v>0.05836212152447793</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3331,19 +3331,19 @@
         </is>
       </c>
       <c r="B81">
-        <v>14.50306795100936</v>
+        <v>14.75868576520493</v>
       </c>
       <c r="C81">
-        <v>0.4967930602925098</v>
+        <v>0.4811084384312426</v>
       </c>
       <c r="D81">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E81">
         <v>2000</v>
       </c>
       <c r="F81">
-        <v>0.09852446785777039</v>
+        <v>0.1003446135790381</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3368,19 +3368,19 @@
         </is>
       </c>
       <c r="B82">
-        <v>29.83470803181835</v>
+        <v>30.60001799368901</v>
       </c>
       <c r="C82">
-        <v>0.8197177063353125</v>
+        <v>0.8116255533046415</v>
       </c>
       <c r="D82">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E82">
         <v>2000</v>
       </c>
       <c r="F82">
-        <v>0.02710614488028776</v>
+        <v>0.02777443240380825</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3405,19 +3405,19 @@
         </is>
       </c>
       <c r="B83">
-        <v>77.71277924009659</v>
+        <v>77.18661655959335</v>
       </c>
       <c r="C83">
-        <v>0.6310144359770035</v>
+        <v>0.6381828662135393</v>
       </c>
       <c r="D83">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E83">
         <v>2000</v>
       </c>
       <c r="F83">
-        <v>0.03235099748407776</v>
+        <v>0.03210668723534844</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3442,19 +3442,19 @@
         </is>
       </c>
       <c r="B84">
-        <v>56.7429273753064</v>
+        <v>56.53442530865419</v>
       </c>
       <c r="C84">
-        <v>0.8259313172772572</v>
+        <v>0.8262364136116782</v>
       </c>
       <c r="D84">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E84">
         <v>2000</v>
       </c>
       <c r="F84">
-        <v>0.05517854116760854</v>
+        <v>0.0549084044255975</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3479,19 +3479,19 @@
         </is>
       </c>
       <c r="B85">
-        <v>29.94126799046387</v>
+        <v>30.36858511674423</v>
       </c>
       <c r="C85">
-        <v>0.8396730478889839</v>
+        <v>0.8312503612139555</v>
       </c>
       <c r="D85">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E85">
         <v>2000</v>
       </c>
       <c r="F85">
-        <v>0.02522518166214296</v>
+        <v>0.0255886291849884</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3516,19 +3516,19 @@
         </is>
       </c>
       <c r="B86">
-        <v>27.49786729955281</v>
+        <v>27.44972501089821</v>
       </c>
       <c r="C86">
-        <v>0.573757343611108</v>
+        <v>0.5851708049119664</v>
       </c>
       <c r="D86">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E86">
         <v>2000</v>
       </c>
       <c r="F86">
-        <v>0.06110270194483538</v>
+        <v>0.06083176360894028</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3553,19 +3553,19 @@
         </is>
       </c>
       <c r="B87">
-        <v>26.4083995238719</v>
+        <v>26.17586267531326</v>
       </c>
       <c r="C87">
-        <v>0.8510380648004027</v>
+        <v>0.8559862445621381</v>
       </c>
       <c r="D87">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E87">
         <v>2000</v>
       </c>
       <c r="F87">
-        <v>0.02251744575531497</v>
+        <v>0.02229124220107295</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3590,19 +3590,19 @@
         </is>
       </c>
       <c r="B88">
-        <v>11.06167165544217</v>
+        <v>11.10599441215571</v>
       </c>
       <c r="C88">
-        <v>0.4900264674296426</v>
+        <v>0.5031930325018064</v>
       </c>
       <c r="D88">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E88">
         <v>2000</v>
       </c>
       <c r="F88">
-        <v>0.09937643589932263</v>
+        <v>0.09916066439424738</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3627,19 +3627,19 @@
         </is>
       </c>
       <c r="B89">
-        <v>18.33323627550209</v>
+        <v>19.05442543978067</v>
       </c>
       <c r="C89">
-        <v>0.4622359743834709</v>
+        <v>0.4279651577166076</v>
       </c>
       <c r="D89">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E89">
         <v>2000</v>
       </c>
       <c r="F89">
-        <v>0.06928094599056044</v>
+        <v>0.07206666202640194</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
         </is>
       </c>
       <c r="B90">
-        <v>32.45985014187748</v>
+        <v>33.44898676382516</v>
       </c>
       <c r="C90">
-        <v>0.783761962571346</v>
+        <v>0.7691715314170778</v>
       </c>
       <c r="D90">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E90">
         <v>2000</v>
       </c>
       <c r="F90">
-        <v>0.04650138245085536</v>
+        <v>0.04788551045614322</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3701,19 +3701,19 @@
         </is>
       </c>
       <c r="B91">
-        <v>14.0842944018151</v>
+        <v>14.31345964796793</v>
       </c>
       <c r="C91">
-        <v>0.4353517499913283</v>
+        <v>0.4258945325417279</v>
       </c>
       <c r="D91">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E91">
         <v>2000</v>
       </c>
       <c r="F91">
-        <v>0.08731153436661789</v>
+        <v>0.08866117224955357</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3738,19 +3738,19 @@
         </is>
       </c>
       <c r="B92">
-        <v>25.38112877730552</v>
+        <v>25.97229617095233</v>
       </c>
       <c r="C92">
-        <v>0.9171086623134536</v>
+        <v>0.9103235674025719</v>
       </c>
       <c r="D92">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E92">
         <v>5000</v>
       </c>
       <c r="F92">
-        <v>0.02095184957712016</v>
+        <v>0.02140103507824022</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3775,19 +3775,19 @@
         </is>
       </c>
       <c r="B93">
-        <v>26.82706211732242</v>
+        <v>26.05804710470522</v>
       </c>
       <c r="C93">
-        <v>0.7815408332331053</v>
+        <v>0.8029437098432657</v>
       </c>
       <c r="D93">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E93">
         <v>5000</v>
       </c>
       <c r="F93">
-        <v>0.04162730269708011</v>
+        <v>0.04023290375602955</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3812,19 +3812,19 @@
         </is>
       </c>
       <c r="B94">
-        <v>23.06981286498977</v>
+        <v>22.46901005814506</v>
       </c>
       <c r="C94">
-        <v>0.7321929417205725</v>
+        <v>0.7497993156984877</v>
       </c>
       <c r="D94">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E94">
         <v>5000</v>
       </c>
       <c r="F94">
-        <v>0.03662896457633495</v>
+        <v>0.03562664117800637</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3849,19 +3849,19 @@
         </is>
       </c>
       <c r="B95">
-        <v>15.56610129523647</v>
+        <v>16.02542698103353</v>
       </c>
       <c r="C95">
-        <v>0.5337144636040847</v>
+        <v>0.5177205384687986</v>
       </c>
       <c r="D95">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E95">
         <v>5000</v>
       </c>
       <c r="F95">
-        <v>0.08838946407669576</v>
+        <v>0.09073735645308126</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3886,19 +3886,19 @@
         </is>
       </c>
       <c r="B96">
-        <v>24.1691562862928</v>
+        <v>24.94915356460648</v>
       </c>
       <c r="C96">
-        <v>0.53546947788334</v>
+        <v>0.5098255081028823</v>
       </c>
       <c r="D96">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E96">
         <v>5000</v>
       </c>
       <c r="F96">
-        <v>0.0431259057963365</v>
+        <v>0.04447581568134355</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3923,19 +3923,19 @@
         </is>
       </c>
       <c r="B97">
-        <v>24.05382532822741</v>
+        <v>24.5329997330092</v>
       </c>
       <c r="C97">
-        <v>0.845706804743365</v>
+        <v>0.8429646729168647</v>
       </c>
       <c r="D97">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E97">
         <v>5000</v>
       </c>
       <c r="F97">
-        <v>0.02231673864454399</v>
+        <v>0.02273566929006524</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3960,19 +3960,19 @@
         </is>
       </c>
       <c r="B98">
-        <v>21.77301617765947</v>
+        <v>21.48155323450321</v>
       </c>
       <c r="C98">
-        <v>0.9279777341316652</v>
+        <v>0.93172793818303</v>
       </c>
       <c r="D98">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E98">
         <v>5000</v>
       </c>
       <c r="F98">
-        <v>0.01635407224062933</v>
+        <v>0.01611906326687818</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3997,19 +3997,19 @@
         </is>
       </c>
       <c r="B99">
-        <v>49.19371900572445</v>
+        <v>49.36405737876493</v>
       </c>
       <c r="C99">
-        <v>0.7045862883539166</v>
+        <v>0.7019443407277264</v>
       </c>
       <c r="D99">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E99">
         <v>5000</v>
       </c>
       <c r="F99">
-        <v>0.03061291852519539</v>
+        <v>0.03069598633143775</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4034,19 +4034,19 @@
         </is>
       </c>
       <c r="B100">
-        <v>51.22082278377652</v>
+        <v>51.58367851553831</v>
       </c>
       <c r="C100">
-        <v>0.6918037358828278</v>
+        <v>0.684647865615105</v>
       </c>
       <c r="D100">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E100">
         <v>5000</v>
       </c>
       <c r="F100">
-        <v>0.02645445138820658</v>
+        <v>0.02663015658713207</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4071,19 +4071,19 @@
         </is>
       </c>
       <c r="B101">
-        <v>58.00738301058543</v>
+        <v>57.82010805027626</v>
       </c>
       <c r="C101">
-        <v>0.89030737845518</v>
+        <v>0.8901405843953253</v>
       </c>
       <c r="D101">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E101">
         <v>5000</v>
       </c>
       <c r="F101">
-        <v>0.04014614575707118</v>
+        <v>0.04000321117090438</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4108,19 +4108,19 @@
         </is>
       </c>
       <c r="B102">
-        <v>14.91950714981806</v>
+        <v>15.12357256447225</v>
       </c>
       <c r="C102">
-        <v>0.4891970935412844</v>
+        <v>0.4840517750166889</v>
       </c>
       <c r="D102">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E102">
         <v>5000</v>
       </c>
       <c r="F102">
-        <v>0.08051072187606918</v>
+        <v>0.08146135753629838</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4145,19 +4145,19 @@
         </is>
       </c>
       <c r="B103">
-        <v>24.84729552882285</v>
+        <v>25.10705904498484</v>
       </c>
       <c r="C103">
-        <v>0.8284669419858016</v>
+        <v>0.8285794873681745</v>
       </c>
       <c r="D103">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E103">
         <v>5000</v>
       </c>
       <c r="F103">
-        <v>0.03252551465802641</v>
+        <v>0.03279739137447074</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4182,19 +4182,19 @@
         </is>
       </c>
       <c r="B104">
-        <v>15.3974416765634</v>
+        <v>16.0012297144352</v>
       </c>
       <c r="C104">
-        <v>0.7940153898764142</v>
+        <v>0.7765524758818726</v>
       </c>
       <c r="D104">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E104">
         <v>5000</v>
       </c>
       <c r="F104">
-        <v>0.08576025019311244</v>
+        <v>0.0890804801501366</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
         </is>
       </c>
       <c r="B105">
-        <v>22.43148052849354</v>
+        <v>22.72416439981702</v>
       </c>
       <c r="C105">
-        <v>0.9080254344252875</v>
+        <v>0.9039661883151684</v>
       </c>
       <c r="D105">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E105">
         <v>5000</v>
       </c>
       <c r="F105">
-        <v>0.01808832664009809</v>
+        <v>0.01830586163547804</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4256,19 +4256,19 @@
         </is>
       </c>
       <c r="B106">
-        <v>24.99154378916261</v>
+        <v>24.86464645863689</v>
       </c>
       <c r="C106">
-        <v>0.8994279943252369</v>
+        <v>0.9000949557481184</v>
       </c>
       <c r="D106">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E106">
         <v>5000</v>
       </c>
       <c r="F106">
-        <v>0.02044004332984851</v>
+        <v>0.02031668810421474</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4293,19 +4293,19 @@
         </is>
       </c>
       <c r="B107">
-        <v>25.40471675294659</v>
+        <v>25.626905144078</v>
       </c>
       <c r="C107">
-        <v>0.8947232283249679</v>
+        <v>0.8953107874296512</v>
       </c>
       <c r="D107">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E107">
         <v>5000</v>
       </c>
       <c r="F107">
-        <v>0.01886022030656762</v>
+        <v>0.01902630085237282</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4330,19 +4330,19 @@
         </is>
       </c>
       <c r="B108">
-        <v>22.85273066468933</v>
+        <v>22.41504332644575</v>
       </c>
       <c r="C108">
-        <v>0.8997155361322515</v>
+        <v>0.904923771032984</v>
       </c>
       <c r="D108">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E108">
         <v>5000</v>
       </c>
       <c r="F108">
-        <v>0.02094633144468954</v>
+        <v>0.02051131940170852</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4367,19 +4367,19 @@
         </is>
       </c>
       <c r="B109">
-        <v>31.19773899287437</v>
+        <v>31.17211922430932</v>
       </c>
       <c r="C109">
-        <v>0.6914194923931566</v>
+        <v>0.6925500046924922</v>
       </c>
       <c r="D109">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E109">
         <v>5000</v>
       </c>
       <c r="F109">
-        <v>0.08884482145363491</v>
+        <v>0.08864109732031085</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4404,19 +4404,19 @@
         </is>
       </c>
       <c r="B110">
-        <v>26.31822657462407</v>
+        <v>25.87666753683429</v>
       </c>
       <c r="C110">
-        <v>0.7142496820383331</v>
+        <v>0.7296564868818122</v>
       </c>
       <c r="D110">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E110">
         <v>5000</v>
       </c>
       <c r="F110">
-        <v>0.05195680200944887</v>
+        <v>0.05097578444165191</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="B111">
-        <v>13.42323250646425</v>
+        <v>13.76029671834671</v>
       </c>
       <c r="C111">
-        <v>0.5508208548674104</v>
+        <v>0.5257132762774906</v>
       </c>
       <c r="D111">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E111">
         <v>5000</v>
       </c>
       <c r="F111">
-        <v>0.09118876392897772</v>
+        <v>0.09355654554219951</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="B112">
-        <v>22.48687835144256</v>
+        <v>22.40626644728025</v>
       </c>
       <c r="C112">
-        <v>0.8987944543043492</v>
+        <v>0.9008028415423975</v>
       </c>
       <c r="D112">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E112">
         <v>5000</v>
       </c>
       <c r="F112">
-        <v>0.02043031833425518</v>
+        <v>0.02033728650061743</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="B113">
-        <v>79.99369768478725</v>
+        <v>76.4065939984369</v>
       </c>
       <c r="C113">
-        <v>0.6053080350848383</v>
+        <v>0.6400362969539755</v>
       </c>
       <c r="D113">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E113">
         <v>5000</v>
       </c>
       <c r="F113">
-        <v>0.03330051939781086</v>
+        <v>0.03178222761366999</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4552,19 +4552,19 @@
         </is>
       </c>
       <c r="B114">
-        <v>41.0832703632281</v>
+        <v>41.64675111829788</v>
       </c>
       <c r="C114">
-        <v>0.9101024750974381</v>
+        <v>0.9082965246479052</v>
       </c>
       <c r="D114">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E114">
         <v>5000</v>
       </c>
       <c r="F114">
-        <v>0.03995061640094194</v>
+        <v>0.0404489236590091</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4589,19 +4589,19 @@
         </is>
       </c>
       <c r="B115">
-        <v>22.24712317135883</v>
+        <v>23.10487559090571</v>
       </c>
       <c r="C115">
-        <v>0.9166482015624681</v>
+        <v>0.9089897837883441</v>
       </c>
       <c r="D115">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E115">
         <v>5000</v>
       </c>
       <c r="F115">
-        <v>0.01874295115478515</v>
+        <v>0.0194682133391521</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4626,19 +4626,19 @@
         </is>
       </c>
       <c r="B116">
-        <v>24.20769531985455</v>
+        <v>25.3591944154703</v>
       </c>
       <c r="C116">
-        <v>0.6508491886730021</v>
+        <v>0.6357586042969956</v>
       </c>
       <c r="D116">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E116">
         <v>5000</v>
       </c>
       <c r="F116">
-        <v>0.05379164775897054</v>
+        <v>0.05619890615962748</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4663,19 +4663,19 @@
         </is>
       </c>
       <c r="B117">
-        <v>19.33074089791536</v>
+        <v>19.92025619633351</v>
       </c>
       <c r="C117">
-        <v>0.9211798515929954</v>
+        <v>0.9177331054956283</v>
       </c>
       <c r="D117">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E117">
         <v>5000</v>
       </c>
       <c r="F117">
-        <v>0.01648259331980293</v>
+        <v>0.0169639969879075</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="B118">
-        <v>9.79567011286094</v>
+        <v>10.02731364286897</v>
       </c>
       <c r="C118">
-        <v>0.5658034714199282</v>
+        <v>0.5669186958668367</v>
       </c>
       <c r="D118">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E118">
         <v>5000</v>
       </c>
       <c r="F118">
-        <v>0.08800286370665407</v>
+        <v>0.08952958609704441</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4737,19 +4737,19 @@
         </is>
       </c>
       <c r="B119">
-        <v>17.70237559531322</v>
+        <v>17.42934986252549</v>
       </c>
       <c r="C119">
-        <v>0.4770302404298991</v>
+        <v>0.4915428726417814</v>
       </c>
       <c r="D119">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E119">
         <v>5000</v>
       </c>
       <c r="F119">
-        <v>0.06689693565790922</v>
+        <v>0.06592038525917358</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4774,19 +4774,19 @@
         </is>
       </c>
       <c r="B120">
-        <v>26.27007631103873</v>
+        <v>27.38408129127928</v>
       </c>
       <c r="C120">
-        <v>0.8586865264178797</v>
+        <v>0.844019068400068</v>
       </c>
       <c r="D120">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E120">
         <v>5000</v>
       </c>
       <c r="F120">
-        <v>0.03763402665795888</v>
+        <v>0.03920300247849636</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4811,19 +4811,19 @@
         </is>
       </c>
       <c r="B121">
-        <v>13.2607277343684</v>
+        <v>13.53429356013628</v>
       </c>
       <c r="C121">
-        <v>0.475244970831814</v>
+        <v>0.4588323970111799</v>
       </c>
       <c r="D121">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E121">
         <v>5000</v>
       </c>
       <c r="F121">
-        <v>0.08220606956046426</v>
+        <v>0.08383482135862412</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4848,19 +4848,19 @@
         </is>
       </c>
       <c r="B122">
-        <v>22.44866795437864</v>
+        <v>19.6470097465439</v>
       </c>
       <c r="C122">
-        <v>0.9353987143268009</v>
+        <v>0.9507338131663958</v>
       </c>
       <c r="D122">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E122">
         <v>10000</v>
       </c>
       <c r="F122">
-        <v>0.01853113462027794</v>
+        <v>0.01618903242134468</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4885,19 +4885,19 @@
         </is>
       </c>
       <c r="B123">
-        <v>23.74570013505444</v>
+        <v>20.76316350077656</v>
       </c>
       <c r="C123">
-        <v>0.8304999575066855</v>
+        <v>0.8790019799145369</v>
       </c>
       <c r="D123">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E123">
         <v>10000</v>
       </c>
       <c r="F123">
-        <v>0.03684598197719704</v>
+        <v>0.03205774997031954</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4922,19 +4922,19 @@
         </is>
       </c>
       <c r="B124">
-        <v>19.93415095606923</v>
+        <v>17.93108374286131</v>
       </c>
       <c r="C124">
-        <v>0.80192614234466</v>
+        <v>0.8414987488248228</v>
       </c>
       <c r="D124">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E124">
         <v>10000</v>
       </c>
       <c r="F124">
-        <v>0.0316503351588629</v>
+        <v>0.02843134988086083</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="B125">
-        <v>14.46887846571639</v>
+        <v>12.78969181268629</v>
       </c>
       <c r="C125">
-        <v>0.5969636278529554</v>
+        <v>0.6950686512698355</v>
       </c>
       <c r="D125">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E125">
         <v>10000</v>
       </c>
       <c r="F125">
-        <v>0.08215907047751787</v>
+        <v>0.07241634349626089</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4996,19 +4996,19 @@
         </is>
       </c>
       <c r="B126">
-        <v>22.71366675475226</v>
+        <v>20.14556374276912</v>
       </c>
       <c r="C126">
-        <v>0.5903278678614082</v>
+        <v>0.682374695946856</v>
       </c>
       <c r="D126">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E126">
         <v>10000</v>
       </c>
       <c r="F126">
-        <v>0.04052882281663935</v>
+        <v>0.03591265641537564</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5033,19 +5033,19 @@
         </is>
       </c>
       <c r="B127">
-        <v>23.52801242394817</v>
+        <v>21.93147805278265</v>
       </c>
       <c r="C127">
-        <v>0.8539200349788664</v>
+        <v>0.8773387755284885</v>
       </c>
       <c r="D127">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E127">
         <v>10000</v>
       </c>
       <c r="F127">
-        <v>0.02182889818671219</v>
+        <v>0.02032473963546688</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5070,19 +5070,19 @@
         </is>
       </c>
       <c r="B128">
-        <v>19.5797066404405</v>
+        <v>18.12684930155194</v>
       </c>
       <c r="C128">
-        <v>0.9433125093436622</v>
+        <v>0.953141277763296</v>
       </c>
       <c r="D128">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E128">
         <v>10000</v>
       </c>
       <c r="F128">
-        <v>0.01470664120374134</v>
+        <v>0.0136018018590749</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5107,19 +5107,19 @@
         </is>
       </c>
       <c r="B129">
-        <v>46.63567761250972</v>
+        <v>45.75608002833609</v>
       </c>
       <c r="C129">
-        <v>0.7399171683436319</v>
+        <v>0.7472321425772948</v>
       </c>
       <c r="D129">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E129">
         <v>10000</v>
       </c>
       <c r="F129">
-        <v>0.02902106667220889</v>
+        <v>0.02845244256065073</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5144,19 +5144,19 @@
         </is>
       </c>
       <c r="B130">
-        <v>49.67317272656491</v>
+        <v>48.99152286135079</v>
       </c>
       <c r="C130">
-        <v>0.7090568402200689</v>
+        <v>0.7170582018454653</v>
       </c>
       <c r="D130">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E130">
         <v>10000</v>
       </c>
       <c r="F130">
-        <v>0.02565512347859269</v>
+        <v>0.0252919520822238</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5181,19 +5181,19 @@
         </is>
       </c>
       <c r="B131">
-        <v>54.03059071803303</v>
+        <v>50.87226945859783</v>
       </c>
       <c r="C131">
-        <v>0.9074046073819674</v>
+        <v>0.9155289333882149</v>
       </c>
       <c r="D131">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E131">
         <v>10000</v>
       </c>
       <c r="F131">
-        <v>0.03739386019036544</v>
+        <v>0.03519630465107226</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5218,19 +5218,19 @@
         </is>
       </c>
       <c r="B132">
-        <v>14.54690509495489</v>
+        <v>13.14280898854839</v>
       </c>
       <c r="C132">
-        <v>0.5084888055826283</v>
+        <v>0.596100107741056</v>
       </c>
       <c r="D132">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E132">
         <v>10000</v>
       </c>
       <c r="F132">
-        <v>0.07850003478645536</v>
+        <v>0.07079220584179323</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5255,19 +5255,19 @@
         </is>
       </c>
       <c r="B133">
-        <v>22.70661541539257</v>
+        <v>20.7271699863652</v>
       </c>
       <c r="C133">
-        <v>0.8551935082335103</v>
+        <v>0.887935749557477</v>
       </c>
       <c r="D133">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E133">
         <v>10000</v>
       </c>
       <c r="F133">
-        <v>0.02972332951370134</v>
+        <v>0.02707593529413367</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5292,19 +5292,19 @@
         </is>
       </c>
       <c r="B134">
-        <v>13.9282396485226</v>
+        <v>12.90452482424054</v>
       </c>
       <c r="C134">
-        <v>0.832306100170813</v>
+        <v>0.8548905424708921</v>
       </c>
       <c r="D134">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E134">
         <v>10000</v>
       </c>
       <c r="F134">
-        <v>0.07757712885674184</v>
+        <v>0.07184080773589968</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5329,19 +5329,19 @@
         </is>
       </c>
       <c r="B135">
-        <v>21.04081838393516</v>
+        <v>18.09450236437971</v>
       </c>
       <c r="C135">
-        <v>0.9222351926634125</v>
+        <v>0.9458157265311078</v>
       </c>
       <c r="D135">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E135">
         <v>10000</v>
       </c>
       <c r="F135">
-        <v>0.01696692267905154</v>
+        <v>0.01457635364791818</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5366,19 +5366,19 @@
         </is>
       </c>
       <c r="B136">
-        <v>22.77191943398406</v>
+        <v>20.47139152603192</v>
       </c>
       <c r="C136">
-        <v>0.9185963410254931</v>
+        <v>0.935933797507052</v>
       </c>
       <c r="D136">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E136">
         <v>10000</v>
       </c>
       <c r="F136">
-        <v>0.01862466055963682</v>
+        <v>0.01672699740113079</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5403,19 +5403,19 @@
         </is>
       </c>
       <c r="B137">
-        <v>23.54576754805771</v>
+        <v>21.70628082037232</v>
       </c>
       <c r="C137">
-        <v>0.9167783115075535</v>
+        <v>0.9309493855417363</v>
       </c>
       <c r="D137">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E137">
         <v>10000</v>
       </c>
       <c r="F137">
-        <v>0.0174801540817058</v>
+        <v>0.01611549373412847</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5440,19 +5440,19 @@
         </is>
       </c>
       <c r="B138">
-        <v>20.93522186395379</v>
+        <v>19.80139542826132</v>
       </c>
       <c r="C138">
-        <v>0.9147693003790219</v>
+        <v>0.9277368304168814</v>
       </c>
       <c r="D138">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E138">
         <v>10000</v>
       </c>
       <c r="F138">
-        <v>0.01918878327779254</v>
+        <v>0.01811965028635082</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5477,19 +5477,19 @@
         </is>
       </c>
       <c r="B139">
-        <v>29.11844540411814</v>
+        <v>27.48143790944671</v>
       </c>
       <c r="C139">
-        <v>0.7285081259112198</v>
+        <v>0.7592655227625906</v>
       </c>
       <c r="D139">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E139">
         <v>10000</v>
       </c>
       <c r="F139">
-        <v>0.08292341581315153</v>
+        <v>0.07814626893681528</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5514,19 +5514,19 @@
         </is>
       </c>
       <c r="B140">
-        <v>23.46022863402686</v>
+        <v>21.76933907772951</v>
       </c>
       <c r="C140">
-        <v>0.7735376365840383</v>
+        <v>0.8127880109819413</v>
       </c>
       <c r="D140">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E140">
         <v>10000</v>
       </c>
       <c r="F140">
-        <v>0.04631461207229718</v>
+        <v>0.04288454588226816</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5551,19 +5551,19 @@
         </is>
       </c>
       <c r="B141">
-        <v>12.26022820002804</v>
+        <v>11.51312896905346</v>
       </c>
       <c r="C141">
-        <v>0.6274552945458542</v>
+        <v>0.677270197965919</v>
       </c>
       <c r="D141">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E141">
         <v>10000</v>
       </c>
       <c r="F141">
-        <v>0.0832880645186886</v>
+        <v>0.07827800495684975</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5588,19 +5588,19 @@
         </is>
       </c>
       <c r="B142">
-        <v>21.11145817724772</v>
+        <v>19.8071431002239</v>
       </c>
       <c r="C142">
-        <v>0.9109432862122745</v>
+        <v>0.922205826994458</v>
       </c>
       <c r="D142">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E142">
         <v>10000</v>
       </c>
       <c r="F142">
-        <v>0.01918068859183453</v>
+        <v>0.01797816449856944</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5625,19 +5625,19 @@
         </is>
       </c>
       <c r="B143">
-        <v>79.64625918839367</v>
+        <v>83.76445214492952</v>
       </c>
       <c r="C143">
-        <v>0.6037816210636834</v>
+        <v>0.5875067350421147</v>
       </c>
       <c r="D143">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E143">
         <v>10000</v>
       </c>
       <c r="F143">
-        <v>0.03315588447376607</v>
+        <v>0.03484281584465053</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5662,19 +5662,19 @@
         </is>
       </c>
       <c r="B144">
-        <v>35.94787724114801</v>
+        <v>33.18986764242325</v>
       </c>
       <c r="C144">
-        <v>0.9331761321920039</v>
+        <v>0.9419501751186524</v>
       </c>
       <c r="D144">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E144">
         <v>10000</v>
       </c>
       <c r="F144">
-        <v>0.03495680459203859</v>
+        <v>0.03223527373618244</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5699,19 +5699,19 @@
         </is>
       </c>
       <c r="B145">
-        <v>20.03242600343641</v>
+        <v>18.19465118662526</v>
       </c>
       <c r="C145">
-        <v>0.9339194574985663</v>
+        <v>0.9469957858708172</v>
       </c>
       <c r="D145">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E145">
         <v>10000</v>
       </c>
       <c r="F145">
-        <v>0.01687709368992195</v>
+        <v>0.01533084865741933</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -5736,19 +5736,19 @@
         </is>
       </c>
       <c r="B146">
-        <v>23.02236987103595</v>
+        <v>21.56861703392885</v>
       </c>
       <c r="C146">
-        <v>0.68140152134895</v>
+        <v>0.7322174795851624</v>
       </c>
       <c r="D146">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E146">
         <v>10000</v>
       </c>
       <c r="F146">
-        <v>0.05115774939813406</v>
+        <v>0.0477985485194771</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5773,19 +5773,19 @@
         </is>
       </c>
       <c r="B147">
-        <v>16.7905957477492</v>
+        <v>15.32016580480633</v>
       </c>
       <c r="C147">
-        <v>0.9423592540941944</v>
+        <v>0.9543672372605995</v>
       </c>
       <c r="D147">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E147">
         <v>10000</v>
       </c>
       <c r="F147">
-        <v>0.01431670740241558</v>
+        <v>0.01304658153015186</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="B148">
-        <v>9.442434906036231</v>
+        <v>8.588367201403701</v>
       </c>
       <c r="C148">
-        <v>0.5952175203011146</v>
+        <v>0.6902809346686061</v>
       </c>
       <c r="D148">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E148">
         <v>10000</v>
       </c>
       <c r="F148">
-        <v>0.08482945041236872</v>
+        <v>0.07668185001253304</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5847,19 +5847,19 @@
         </is>
       </c>
       <c r="B149">
-        <v>16.70828811999575</v>
+        <v>16.47536300358017</v>
       </c>
       <c r="C149">
-        <v>0.5216299552647954</v>
+        <v>0.5323224429473945</v>
       </c>
       <c r="D149">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E149">
         <v>10000</v>
       </c>
       <c r="F149">
-        <v>0.06314029827799435</v>
+        <v>0.06231226552034861</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5884,19 +5884,19 @@
         </is>
       </c>
       <c r="B150">
-        <v>23.55670265061412</v>
+        <v>21.70749097641382</v>
       </c>
       <c r="C150">
-        <v>0.8876731418282053</v>
+        <v>0.9040971105032137</v>
       </c>
       <c r="D150">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E150">
         <v>10000</v>
       </c>
       <c r="F150">
-        <v>0.03374689761195325</v>
+        <v>0.03107640579570208</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5921,19 +5921,19 @@
         </is>
       </c>
       <c r="B151">
-        <v>12.14164135992036</v>
+        <v>10.85839488278926</v>
       </c>
       <c r="C151">
-        <v>0.5539911779619598</v>
+        <v>0.6467405227469533</v>
       </c>
       <c r="D151">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E151">
         <v>10000</v>
       </c>
       <c r="F151">
-        <v>0.07526861528307839</v>
+        <v>0.06725963133541416</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
